--- a/data/07_QUARTERLY_WEIGHTING/2024/T4/444X_1D/LFS_KNOWN_TOTALS_2024_T4_444X_1D.xlsx
+++ b/data/07_QUARTERLY_WEIGHTING/2024/T4/444X_1D/LFS_KNOWN_TOTALS_2024_T4_444X_1D.xlsx
@@ -2741,1174 +2741,1174 @@
         <v>1065011</v>
       </c>
       <c r="BA2">
+        <v>28606</v>
+      </c>
+      <c r="BB2">
+        <v>31552</v>
+      </c>
+      <c r="BC2">
+        <v>30298</v>
+      </c>
+      <c r="BD2">
         <v>1035453</v>
       </c>
-      <c r="BB2">
+      <c r="BE2">
         <v>1438086</v>
       </c>
-      <c r="BC2">
+      <c r="BF2">
         <v>894739</v>
       </c>
-      <c r="BD2">
+      <c r="BG2">
+        <v>28756</v>
+      </c>
+      <c r="BH2">
+        <v>32177</v>
+      </c>
+      <c r="BI2">
+        <v>24291</v>
+      </c>
+      <c r="BJ2">
         <v>153622</v>
       </c>
-      <c r="BE2">
+      <c r="BK2">
         <v>155542</v>
       </c>
-      <c r="BF2">
+      <c r="BL2">
         <v>101726</v>
       </c>
-      <c r="BG2">
+      <c r="BM2">
+        <v>228138</v>
+      </c>
+      <c r="BN2">
+        <v>168754</v>
+      </c>
+      <c r="BO2">
+        <v>141432</v>
+      </c>
+      <c r="BP2">
         <v>150819</v>
       </c>
-      <c r="BH2">
+      <c r="BQ2">
         <v>156047</v>
       </c>
-      <c r="BI2">
+      <c r="BR2">
         <v>86692</v>
       </c>
-      <c r="BJ2">
+      <c r="BS2">
+        <v>210806</v>
+      </c>
+      <c r="BT2">
+        <v>166502</v>
+      </c>
+      <c r="BU2">
+        <v>115978</v>
+      </c>
+      <c r="BV2">
         <v>112454</v>
       </c>
-      <c r="BK2">
+      <c r="BW2">
         <v>114750</v>
       </c>
-      <c r="BL2">
+      <c r="BX2">
         <v>73389</v>
       </c>
-      <c r="BM2">
+      <c r="BY2">
+        <v>121106</v>
+      </c>
+      <c r="BZ2">
+        <v>80839</v>
+      </c>
+      <c r="CA2">
+        <v>61913</v>
+      </c>
+      <c r="CB2">
         <v>116539</v>
       </c>
-      <c r="BN2">
+      <c r="CC2">
         <v>118646</v>
       </c>
-      <c r="BO2">
+      <c r="CD2">
         <v>67328</v>
       </c>
-      <c r="BP2">
+      <c r="CE2">
+        <v>120156</v>
+      </c>
+      <c r="CF2">
+        <v>91080</v>
+      </c>
+      <c r="CG2">
+        <v>70780</v>
+      </c>
+      <c r="CH2">
         <v>154331</v>
       </c>
-      <c r="BQ2">
+      <c r="CI2">
         <v>182196</v>
       </c>
-      <c r="BR2">
+      <c r="CJ2">
         <v>113676</v>
       </c>
-      <c r="BS2">
+      <c r="CK2">
+        <v>117988</v>
+      </c>
+      <c r="CL2">
+        <v>78755</v>
+      </c>
+      <c r="CM2">
+        <v>74731</v>
+      </c>
+      <c r="CN2">
         <v>154756</v>
       </c>
-      <c r="BT2">
+      <c r="CO2">
         <v>177800</v>
       </c>
-      <c r="BU2">
+      <c r="CP2">
         <v>103797</v>
       </c>
-      <c r="BV2">
+      <c r="CQ2">
+        <v>109396</v>
+      </c>
+      <c r="CR2">
+        <v>73552</v>
+      </c>
+      <c r="CS2">
+        <v>91933</v>
+      </c>
+      <c r="CT2">
         <v>61378</v>
       </c>
-      <c r="BW2">
+      <c r="CU2">
         <v>68839</v>
       </c>
-      <c r="BX2">
+      <c r="CV2">
         <v>47996</v>
       </c>
-      <c r="BY2">
+      <c r="CW2">
+        <v>87265</v>
+      </c>
+      <c r="CX2">
+        <v>74113</v>
+      </c>
+      <c r="CY2">
+        <v>59840</v>
+      </c>
+      <c r="CZ2">
         <v>61307</v>
       </c>
-      <c r="BZ2">
+      <c r="DA2">
         <v>68599</v>
       </c>
-      <c r="CA2">
+      <c r="DB2">
         <v>42697</v>
       </c>
-      <c r="CB2">
+      <c r="DC2">
+        <v>81487</v>
+      </c>
+      <c r="DD2">
+        <v>67391</v>
+      </c>
+      <c r="DE2">
+        <v>46324</v>
+      </c>
+      <c r="DF2">
         <v>108291</v>
       </c>
-      <c r="CC2">
+      <c r="DG2">
         <v>102891</v>
       </c>
-      <c r="CD2">
+      <c r="DH2">
         <v>69513</v>
       </c>
-      <c r="CE2">
+      <c r="DI2">
+        <v>215925</v>
+      </c>
+      <c r="DJ2">
+        <v>157730</v>
+      </c>
+      <c r="DK2">
+        <v>130607</v>
+      </c>
+      <c r="DL2">
         <v>103529</v>
       </c>
-      <c r="CF2">
+      <c r="DM2">
         <v>100553</v>
       </c>
-      <c r="CG2">
+      <c r="DN2">
         <v>58871</v>
       </c>
-      <c r="CH2">
+      <c r="DO2">
+        <v>198574</v>
+      </c>
+      <c r="DP2">
+        <v>155808</v>
+      </c>
+      <c r="DQ2">
+        <v>102975</v>
+      </c>
+      <c r="DR2">
         <v>48843</v>
       </c>
-      <c r="CI2">
+      <c r="DS2">
         <v>62835</v>
       </c>
-      <c r="CJ2">
+      <c r="DT2">
         <v>42751</v>
       </c>
-      <c r="CK2">
+      <c r="DU2">
+        <v>25814</v>
+      </c>
+      <c r="DV2">
+        <v>22963</v>
+      </c>
+      <c r="DW2">
+        <v>21697</v>
+      </c>
+      <c r="DX2">
         <v>52389</v>
       </c>
-      <c r="CL2">
+      <c r="DY2">
         <v>65138</v>
       </c>
-      <c r="CM2">
+      <c r="DZ2">
         <v>40014</v>
       </c>
-      <c r="CN2">
+      <c r="EA2">
+        <v>23751</v>
+      </c>
+      <c r="EB2">
+        <v>20350</v>
+      </c>
+      <c r="EC2">
+        <v>21671</v>
+      </c>
+      <c r="ED2">
         <v>49603</v>
       </c>
-      <c r="CO2">
+      <c r="EE2">
         <v>57775</v>
       </c>
-      <c r="CP2">
+      <c r="EF2">
         <v>34107</v>
       </c>
-      <c r="CQ2">
+      <c r="EG2">
+        <v>145483</v>
+      </c>
+      <c r="EH2">
+        <v>114435</v>
+      </c>
+      <c r="EI2">
+        <v>89879</v>
+      </c>
+      <c r="EJ2">
         <v>49540</v>
       </c>
-      <c r="CR2">
+      <c r="EK2">
         <v>56155</v>
       </c>
-      <c r="CS2">
+      <c r="EL2">
         <v>34956</v>
       </c>
-      <c r="CT2">
+      <c r="EM2">
+        <v>136439</v>
+      </c>
+      <c r="EN2">
+        <v>112449</v>
+      </c>
+      <c r="EO2">
+        <v>97966</v>
+      </c>
+      <c r="EP2">
         <v>87456</v>
       </c>
-      <c r="CU2">
+      <c r="EQ2">
         <v>93840</v>
       </c>
-      <c r="CV2">
+      <c r="ER2">
         <v>65550</v>
       </c>
-      <c r="CW2">
+      <c r="ES2">
+        <v>137274</v>
+      </c>
+      <c r="ET2">
+        <v>121550</v>
+      </c>
+      <c r="EU2">
+        <v>96574</v>
+      </c>
+      <c r="EV2">
         <v>88018</v>
       </c>
-      <c r="CX2">
+      <c r="EW2">
         <v>94718</v>
       </c>
-      <c r="CY2">
+      <c r="EX2">
         <v>47845</v>
       </c>
-      <c r="CZ2">
+      <c r="EY2">
+        <v>133732</v>
+      </c>
+      <c r="EZ2">
+        <v>113365</v>
+      </c>
+      <c r="FA2">
+        <v>62546</v>
+      </c>
+      <c r="FB2">
         <v>25076</v>
       </c>
-      <c r="DA2">
+      <c r="FC2">
         <v>23026</v>
       </c>
-      <c r="DB2">
+      <c r="FD2">
         <v>15580</v>
       </c>
-      <c r="DC2">
+      <c r="FE2">
+        <v>44150</v>
+      </c>
+      <c r="FF2">
+        <v>27697</v>
+      </c>
+      <c r="FG2">
+        <v>22767</v>
+      </c>
+      <c r="FH2">
         <v>24122</v>
       </c>
-      <c r="DD2">
+      <c r="FI2">
         <v>22050</v>
       </c>
-      <c r="DE2">
+      <c r="FJ2">
         <v>13355</v>
       </c>
-      <c r="DF2">
+      <c r="FK2">
+        <v>41305</v>
+      </c>
+      <c r="FL2">
+        <v>28602</v>
+      </c>
+      <c r="FM2">
+        <v>23246</v>
+      </c>
+      <c r="FN2">
         <v>15740</v>
       </c>
-      <c r="DG2">
+      <c r="FO2">
         <v>17073</v>
       </c>
-      <c r="DH2">
+      <c r="FP2">
         <v>11477</v>
       </c>
-      <c r="DI2">
+      <c r="FQ2">
+        <v>36778</v>
+      </c>
+      <c r="FR2">
+        <v>23715</v>
+      </c>
+      <c r="FS2">
+        <v>26729</v>
+      </c>
+      <c r="FT2">
         <v>16241</v>
       </c>
-      <c r="DJ2">
+      <c r="FU2">
         <v>16665</v>
       </c>
-      <c r="DK2">
+      <c r="FV2">
         <v>13453</v>
       </c>
-      <c r="DL2">
+      <c r="FW2">
+        <v>34798</v>
+      </c>
+      <c r="FX2">
+        <v>21252</v>
+      </c>
+      <c r="FY2">
+        <v>33003</v>
+      </c>
+      <c r="FZ2">
         <v>88490</v>
       </c>
-      <c r="DM2">
+      <c r="GA2">
         <v>85843</v>
       </c>
-      <c r="DN2">
+      <c r="GB2">
         <v>58231</v>
       </c>
-      <c r="DO2">
+      <c r="GC2">
+        <v>130557</v>
+      </c>
+      <c r="GD2">
+        <v>95548</v>
+      </c>
+      <c r="GE2">
+        <v>84836</v>
+      </c>
+      <c r="GF2">
         <v>84930</v>
       </c>
-      <c r="DP2">
+      <c r="GG2">
         <v>82279</v>
       </c>
-      <c r="DQ2">
+      <c r="GH2">
         <v>51736</v>
       </c>
-      <c r="DR2">
+      <c r="GI2">
+        <v>120597</v>
+      </c>
+      <c r="GJ2">
+        <v>91507</v>
+      </c>
+      <c r="GK2">
+        <v>72646</v>
+      </c>
+      <c r="GL2">
         <v>63228</v>
       </c>
-      <c r="DS2">
+      <c r="GM2">
         <v>69097</v>
       </c>
-      <c r="DT2">
+      <c r="GN2">
         <v>57540</v>
       </c>
-      <c r="DU2">
+      <c r="GO2">
+        <v>87421</v>
+      </c>
+      <c r="GP2">
+        <v>75923</v>
+      </c>
+      <c r="GQ2">
+        <v>70468</v>
+      </c>
+      <c r="GR2">
         <v>63206</v>
       </c>
-      <c r="DV2">
+      <c r="GS2">
         <v>74621</v>
       </c>
-      <c r="DW2">
+      <c r="GT2">
         <v>51948</v>
       </c>
-      <c r="DX2">
+      <c r="GU2">
+        <v>85658</v>
+      </c>
+      <c r="GV2">
+        <v>76592</v>
+      </c>
+      <c r="GW2">
+        <v>58221</v>
+      </c>
+      <c r="GX2">
         <v>31343</v>
       </c>
-      <c r="DY2">
+      <c r="GY2">
         <v>27157</v>
       </c>
-      <c r="DZ2">
+      <c r="GZ2">
         <v>20286</v>
       </c>
-      <c r="EA2">
+      <c r="HA2">
+        <v>75703</v>
+      </c>
+      <c r="HB2">
+        <v>51359</v>
+      </c>
+      <c r="HC2">
+        <v>40208</v>
+      </c>
+      <c r="HD2">
         <v>30962</v>
       </c>
-      <c r="EB2">
+      <c r="HE2">
         <v>27628</v>
       </c>
-      <c r="EC2">
+      <c r="HF2">
         <v>16447</v>
       </c>
-      <c r="ED2">
+      <c r="HG2">
+        <v>72072</v>
+      </c>
+      <c r="HH2">
+        <v>55554</v>
+      </c>
+      <c r="HI2">
+        <v>31042</v>
+      </c>
+      <c r="HJ2">
         <v>94153</v>
       </c>
-      <c r="EE2">
+      <c r="HK2">
         <v>94536</v>
       </c>
-      <c r="EF2">
+      <c r="HL2">
         <v>62956</v>
       </c>
-      <c r="EG2">
+      <c r="HM2">
+        <v>146755</v>
+      </c>
+      <c r="HN2">
+        <v>104274</v>
+      </c>
+      <c r="HO2">
+        <v>103329</v>
+      </c>
+      <c r="HP2">
         <v>93692</v>
       </c>
-      <c r="EH2">
+      <c r="HQ2">
         <v>93283</v>
       </c>
-      <c r="EI2">
+      <c r="HR2">
         <v>56577</v>
       </c>
-      <c r="EJ2">
+      <c r="HS2">
+        <v>142211</v>
+      </c>
+      <c r="HT2">
+        <v>108142</v>
+      </c>
+      <c r="HU2">
+        <v>83832</v>
+      </c>
+      <c r="HV2">
         <v>74063</v>
       </c>
-      <c r="EK2">
+      <c r="HW2">
         <v>76867</v>
       </c>
-      <c r="EL2">
+      <c r="HX2">
         <v>61029</v>
       </c>
-      <c r="EM2">
+      <c r="HY2">
+        <v>98438</v>
+      </c>
+      <c r="HZ2">
+        <v>87525</v>
+      </c>
+      <c r="IA2">
+        <v>81910</v>
+      </c>
+      <c r="IB2">
         <v>74064</v>
       </c>
-      <c r="EN2">
+      <c r="IC2">
         <v>76622</v>
       </c>
-      <c r="EO2">
+      <c r="ID2">
         <v>54843</v>
       </c>
-      <c r="EP2">
+      <c r="IE2">
+        <v>94635</v>
+      </c>
+      <c r="IF2">
+        <v>79012</v>
+      </c>
+      <c r="IG2">
+        <v>68002</v>
+      </c>
+      <c r="IH2">
         <v>92544</v>
       </c>
-      <c r="EQ2">
+      <c r="II2">
         <v>89869</v>
       </c>
-      <c r="ER2">
+      <c r="IJ2">
         <v>63134</v>
       </c>
-      <c r="ES2">
+      <c r="IK2">
+        <v>122597</v>
+      </c>
+      <c r="IL2">
+        <v>83527</v>
+      </c>
+      <c r="IM2">
+        <v>88003</v>
+      </c>
+      <c r="IN2">
         <v>92979</v>
       </c>
-      <c r="ET2">
+      <c r="IO2">
         <v>91442</v>
       </c>
-      <c r="EU2">
+      <c r="IP2">
         <v>57195</v>
       </c>
-      <c r="EV2">
+      <c r="IQ2">
+        <v>117368</v>
+      </c>
+      <c r="IR2">
+        <v>84337</v>
+      </c>
+      <c r="IS2">
+        <v>72112</v>
+      </c>
+      <c r="IT2">
         <v>61966</v>
       </c>
-      <c r="EW2">
+      <c r="IU2">
         <v>69347</v>
       </c>
-      <c r="EX2">
+      <c r="IV2">
         <v>43873</v>
       </c>
-      <c r="EY2">
+      <c r="IW2">
+        <v>96070</v>
+      </c>
+      <c r="IX2">
+        <v>93480</v>
+      </c>
+      <c r="IY2">
+        <v>61791</v>
+      </c>
+      <c r="IZ2">
         <v>60240</v>
       </c>
-      <c r="EZ2">
+      <c r="JA2">
         <v>61409</v>
       </c>
-      <c r="FA2">
+      <c r="JB2">
         <v>28419</v>
       </c>
-      <c r="FB2">
+      <c r="JC2">
+        <v>86757</v>
+      </c>
+      <c r="JD2">
+        <v>79588</v>
+      </c>
+      <c r="JE2">
+        <v>38405</v>
+      </c>
+      <c r="JF2">
         <v>13977</v>
       </c>
-      <c r="FC2">
+      <c r="JG2">
         <v>11669</v>
       </c>
-      <c r="FD2">
+      <c r="JH2">
         <v>8708</v>
       </c>
-      <c r="FE2">
+      <c r="JI2">
+        <v>48602</v>
+      </c>
+      <c r="JJ2">
+        <v>31910</v>
+      </c>
+      <c r="JK2">
+        <v>29067</v>
+      </c>
+      <c r="JL2">
         <v>13531</v>
       </c>
-      <c r="FF2">
+      <c r="JM2">
         <v>11845</v>
       </c>
-      <c r="FG2">
+      <c r="JN2">
         <v>6909</v>
       </c>
-      <c r="FH2">
+      <c r="JO2">
+        <v>46360</v>
+      </c>
+      <c r="JP2">
+        <v>34699</v>
+      </c>
+      <c r="JQ2">
+        <v>25654</v>
+      </c>
+      <c r="JR2">
         <v>51017</v>
       </c>
-      <c r="FI2">
+      <c r="JS2">
         <v>46250</v>
       </c>
-      <c r="FJ2">
+      <c r="JT2">
         <v>28218</v>
       </c>
-      <c r="FK2">
+      <c r="JU2">
+        <v>72444</v>
+      </c>
+      <c r="JV2">
+        <v>52242</v>
+      </c>
+      <c r="JW2">
+        <v>35022</v>
+      </c>
+      <c r="JX2">
         <v>50958</v>
       </c>
-      <c r="FL2">
+      <c r="JY2">
         <v>47491</v>
       </c>
-      <c r="FM2">
+      <c r="JZ2">
         <v>24900</v>
       </c>
-      <c r="FN2">
+      <c r="KA2">
+        <v>69650</v>
+      </c>
+      <c r="KB2">
+        <v>54680</v>
+      </c>
+      <c r="KC2">
+        <v>36020</v>
+      </c>
+      <c r="KD2">
         <v>28759</v>
       </c>
-      <c r="FO2">
+      <c r="KE2">
         <v>32646</v>
       </c>
-      <c r="FP2">
+      <c r="KF2">
         <v>21485</v>
       </c>
-      <c r="FQ2">
+      <c r="KG2">
+        <v>59378</v>
+      </c>
+      <c r="KH2">
+        <v>37586</v>
+      </c>
+      <c r="KI2">
+        <v>42360</v>
+      </c>
+      <c r="KJ2">
         <v>28763</v>
       </c>
-      <c r="FR2">
+      <c r="KK2">
         <v>30054</v>
       </c>
-      <c r="FS2">
+      <c r="KL2">
         <v>21068</v>
       </c>
-      <c r="FT2">
+      <c r="KM2">
+        <v>56540</v>
+      </c>
+      <c r="KN2">
+        <v>35832</v>
+      </c>
+      <c r="KO2">
+        <v>50786</v>
+      </c>
+      <c r="KP2">
         <v>24860</v>
       </c>
-      <c r="FU2">
+      <c r="KQ2">
         <v>21510</v>
       </c>
-      <c r="FV2">
+      <c r="KR2">
         <v>14350</v>
       </c>
-      <c r="FW2">
+      <c r="KS2">
+        <v>100227</v>
+      </c>
+      <c r="KT2">
+        <v>66376</v>
+      </c>
+      <c r="KU2">
+        <v>50626</v>
+      </c>
+      <c r="KV2">
         <v>23885</v>
       </c>
-      <c r="FX2">
+      <c r="KW2">
         <v>20760</v>
       </c>
-      <c r="FY2">
+      <c r="KX2">
         <v>12542</v>
       </c>
-      <c r="FZ2">
+      <c r="KY2">
+        <v>94208</v>
+      </c>
+      <c r="KZ2">
+        <v>71272</v>
+      </c>
+      <c r="LA2">
+        <v>45630</v>
+      </c>
+      <c r="LB2">
         <v>16737</v>
       </c>
-      <c r="GA2">
+      <c r="LC2">
         <v>16984</v>
       </c>
-      <c r="GB2">
+      <c r="LD2">
         <v>11282</v>
       </c>
-      <c r="GC2">
+      <c r="LE2">
+        <v>91181</v>
+      </c>
+      <c r="LF2">
+        <v>59303</v>
+      </c>
+      <c r="LG2">
+        <v>39027</v>
+      </c>
+      <c r="LH2">
         <v>16595</v>
       </c>
-      <c r="GD2">
+      <c r="LI2">
         <v>17412</v>
       </c>
-      <c r="GE2">
+      <c r="LJ2">
         <v>9937</v>
       </c>
-      <c r="GF2">
+      <c r="LK2">
+        <v>88479</v>
+      </c>
+      <c r="LL2">
+        <v>66391</v>
+      </c>
+      <c r="LM2">
+        <v>40671</v>
+      </c>
+      <c r="LN2">
         <v>7824</v>
       </c>
-      <c r="GG2">
+      <c r="LO2">
         <v>5908</v>
       </c>
-      <c r="GH2">
+      <c r="LP2">
         <v>4225</v>
       </c>
-      <c r="GI2">
+      <c r="LQ2">
+        <v>30503</v>
+      </c>
+      <c r="LR2">
+        <v>19829</v>
+      </c>
+      <c r="LS2">
+        <v>13107</v>
+      </c>
+      <c r="LT2">
         <v>7452</v>
       </c>
-      <c r="GJ2">
+      <c r="LU2">
         <v>5605</v>
       </c>
-      <c r="GK2">
+      <c r="LV2">
         <v>4001</v>
       </c>
-      <c r="GL2">
+      <c r="LW2">
+        <v>29112</v>
+      </c>
+      <c r="LX2">
+        <v>20476</v>
+      </c>
+      <c r="LY2">
+        <v>12911</v>
+      </c>
+      <c r="LZ2">
         <v>25449</v>
       </c>
-      <c r="GM2">
+      <c r="MA2">
         <v>25856</v>
       </c>
-      <c r="GN2">
+      <c r="MB2">
         <v>16928</v>
       </c>
-      <c r="GO2">
+      <c r="MC2">
+        <v>79315</v>
+      </c>
+      <c r="MD2">
+        <v>63798</v>
+      </c>
+      <c r="ME2">
+        <v>53846</v>
+      </c>
+      <c r="MF2">
         <v>24956</v>
       </c>
-      <c r="GP2">
+      <c r="MG2">
         <v>23247</v>
       </c>
-      <c r="GQ2">
+      <c r="MH2">
         <v>12100</v>
       </c>
-      <c r="GR2">
+      <c r="MI2">
+        <v>74829</v>
+      </c>
+      <c r="MJ2">
+        <v>61116</v>
+      </c>
+      <c r="MK2">
+        <v>36923</v>
+      </c>
+      <c r="ML2">
         <v>38160</v>
       </c>
-      <c r="GS2">
+      <c r="MM2">
         <v>40894</v>
       </c>
-      <c r="GT2">
+      <c r="MN2">
         <v>31739</v>
       </c>
-      <c r="GU2">
+      <c r="MO2">
+        <v>50230</v>
+      </c>
+      <c r="MP2">
+        <v>39812</v>
+      </c>
+      <c r="MQ2">
+        <v>42074</v>
+      </c>
+      <c r="MR2">
         <v>38810</v>
       </c>
-      <c r="GV2">
+      <c r="MS2">
         <v>42170</v>
       </c>
-      <c r="GW2">
+      <c r="MT2">
         <v>28325</v>
       </c>
-      <c r="GX2">
+      <c r="MU2">
+        <v>48085</v>
+      </c>
+      <c r="MV2">
+        <v>37651</v>
+      </c>
+      <c r="MW2">
+        <v>36889</v>
+      </c>
+      <c r="MX2">
         <v>73041</v>
       </c>
-      <c r="GY2">
+      <c r="MY2">
         <v>70199</v>
       </c>
-      <c r="GZ2">
+      <c r="MZ2">
         <v>47595</v>
       </c>
-      <c r="HA2">
+      <c r="NA2">
+        <v>139994</v>
+      </c>
+      <c r="NB2">
+        <v>110911</v>
+      </c>
+      <c r="NC2">
+        <v>96878</v>
+      </c>
+      <c r="ND2">
         <v>69075</v>
       </c>
-      <c r="HB2">
+      <c r="NE2">
         <v>67324</v>
       </c>
-      <c r="HC2">
+      <c r="NF2">
         <v>36186</v>
       </c>
-      <c r="HD2">
+      <c r="NG2">
+        <v>128293</v>
+      </c>
+      <c r="NH2">
+        <v>105818</v>
+      </c>
+      <c r="NI2">
+        <v>71496</v>
+      </c>
+      <c r="NJ2">
         <v>49549</v>
       </c>
-      <c r="HE2">
+      <c r="NK2">
         <v>52053</v>
       </c>
-      <c r="HF2">
+      <c r="NL2">
         <v>33653</v>
       </c>
-      <c r="HG2">
+      <c r="NM2">
+        <v>85630</v>
+      </c>
+      <c r="NN2">
+        <v>70742</v>
+      </c>
+      <c r="NO2">
+        <v>54402</v>
+      </c>
+      <c r="NP2">
         <v>49694</v>
       </c>
-      <c r="HH2">
+      <c r="NQ2">
         <v>50727</v>
       </c>
-      <c r="HI2">
+      <c r="NR2">
         <v>30122</v>
       </c>
-      <c r="HJ2">
+      <c r="NS2">
+        <v>81554</v>
+      </c>
+      <c r="NT2">
+        <v>65720</v>
+      </c>
+      <c r="NU2">
+        <v>51107</v>
+      </c>
+      <c r="NV2">
         <v>24649</v>
       </c>
-      <c r="HK2">
+      <c r="NW2">
         <v>27289</v>
       </c>
-      <c r="HL2">
+      <c r="NX2">
         <v>16923</v>
       </c>
-      <c r="HM2">
+      <c r="NY2">
+        <v>56827</v>
+      </c>
+      <c r="NZ2">
+        <v>37174</v>
+      </c>
+      <c r="OA2">
+        <v>40305</v>
+      </c>
+      <c r="OB2">
         <v>24435</v>
       </c>
-      <c r="HN2">
+      <c r="OC2">
         <v>25455</v>
       </c>
-      <c r="HO2">
+      <c r="OD2">
         <v>16635</v>
       </c>
-      <c r="HP2">
+      <c r="OE2">
+        <v>52973</v>
+      </c>
+      <c r="OF2">
+        <v>35499</v>
+      </c>
+      <c r="OG2">
+        <v>44166</v>
+      </c>
+      <c r="OH2">
         <v>61362</v>
       </c>
-      <c r="HQ2">
+      <c r="OI2">
         <v>70918</v>
       </c>
-      <c r="HR2">
+      <c r="OJ2">
         <v>53593</v>
       </c>
-      <c r="HS2">
+      <c r="OK2">
+        <v>74817</v>
+      </c>
+      <c r="OL2">
+        <v>75715</v>
+      </c>
+      <c r="OM2">
+        <v>66688</v>
+      </c>
+      <c r="ON2">
         <v>59140</v>
       </c>
-      <c r="HT2">
+      <c r="OO2">
         <v>68560</v>
       </c>
-      <c r="HU2">
+      <c r="OP2">
         <v>49544</v>
       </c>
-      <c r="HV2">
+      <c r="OQ2">
+        <v>70630</v>
+      </c>
+      <c r="OR2">
+        <v>70424</v>
+      </c>
+      <c r="OS2">
+        <v>63044</v>
+      </c>
+      <c r="OT2">
         <v>83778</v>
       </c>
-      <c r="HW2">
+      <c r="OU2">
         <v>89387</v>
       </c>
-      <c r="HX2">
+      <c r="OV2">
         <v>48746</v>
       </c>
-      <c r="HY2">
+      <c r="OW2">
+        <v>174209</v>
+      </c>
+      <c r="OX2">
+        <v>136401</v>
+      </c>
+      <c r="OY2">
+        <v>112743</v>
+      </c>
+      <c r="OZ2">
         <v>81070</v>
       </c>
-      <c r="HZ2">
+      <c r="PA2">
         <v>84468</v>
       </c>
-      <c r="IA2">
+      <c r="PB2">
         <v>37997</v>
       </c>
-      <c r="IB2">
+      <c r="PC2">
+        <v>169615</v>
+      </c>
+      <c r="PD2">
+        <v>133521</v>
+      </c>
+      <c r="PE2">
+        <v>86116</v>
+      </c>
+      <c r="PF2">
         <v>49839</v>
       </c>
-      <c r="IC2">
+      <c r="PG2">
         <v>46306</v>
       </c>
-      <c r="ID2">
+      <c r="PH2">
         <v>31791</v>
       </c>
-      <c r="IE2">
+      <c r="PI2">
+        <v>97870</v>
+      </c>
+      <c r="PJ2">
+        <v>63845</v>
+      </c>
+      <c r="PK2">
+        <v>45676</v>
+      </c>
+      <c r="PL2">
         <v>50104</v>
       </c>
-      <c r="IF2">
+      <c r="PM2">
         <v>47956</v>
       </c>
-      <c r="IG2">
+      <c r="PN2">
         <v>29045</v>
       </c>
-      <c r="IH2">
+      <c r="PO2">
+        <v>93707</v>
+      </c>
+      <c r="PP2">
+        <v>69490</v>
+      </c>
+      <c r="PQ2">
+        <v>44774</v>
+      </c>
+      <c r="PR2">
         <v>32120</v>
       </c>
-      <c r="II2">
+      <c r="PS2">
         <v>36161</v>
       </c>
-      <c r="IJ2">
+      <c r="PT2">
         <v>26154</v>
       </c>
-      <c r="IK2">
+      <c r="PU2">
+        <v>51625</v>
+      </c>
+      <c r="PV2">
+        <v>53599</v>
+      </c>
+      <c r="PW2">
+        <v>47327</v>
+      </c>
+      <c r="PX2">
         <v>30629</v>
       </c>
-      <c r="IL2">
+      <c r="PY2">
         <v>33548</v>
       </c>
-      <c r="IM2">
+      <c r="PZ2">
         <v>25796</v>
-      </c>
-      <c r="IN2">
-        <v>28606</v>
-      </c>
-      <c r="IO2">
-        <v>31552</v>
-      </c>
-      <c r="IP2">
-        <v>30298</v>
-      </c>
-      <c r="IQ2">
-        <v>28756</v>
-      </c>
-      <c r="IR2">
-        <v>32177</v>
-      </c>
-      <c r="IS2">
-        <v>24291</v>
-      </c>
-      <c r="IT2">
-        <v>228138</v>
-      </c>
-      <c r="IU2">
-        <v>168754</v>
-      </c>
-      <c r="IV2">
-        <v>141432</v>
-      </c>
-      <c r="IW2">
-        <v>210806</v>
-      </c>
-      <c r="IX2">
-        <v>166502</v>
-      </c>
-      <c r="IY2">
-        <v>115978</v>
-      </c>
-      <c r="IZ2">
-        <v>121106</v>
-      </c>
-      <c r="JA2">
-        <v>80839</v>
-      </c>
-      <c r="JB2">
-        <v>61913</v>
-      </c>
-      <c r="JC2">
-        <v>120156</v>
-      </c>
-      <c r="JD2">
-        <v>91080</v>
-      </c>
-      <c r="JE2">
-        <v>70780</v>
-      </c>
-      <c r="JF2">
-        <v>117988</v>
-      </c>
-      <c r="JG2">
-        <v>78755</v>
-      </c>
-      <c r="JH2">
-        <v>74731</v>
-      </c>
-      <c r="JI2">
-        <v>109396</v>
-      </c>
-      <c r="JJ2">
-        <v>73552</v>
-      </c>
-      <c r="JK2">
-        <v>91933</v>
-      </c>
-      <c r="JL2">
-        <v>87265</v>
-      </c>
-      <c r="JM2">
-        <v>74113</v>
-      </c>
-      <c r="JN2">
-        <v>59840</v>
-      </c>
-      <c r="JO2">
-        <v>81487</v>
-      </c>
-      <c r="JP2">
-        <v>67391</v>
-      </c>
-      <c r="JQ2">
-        <v>46324</v>
-      </c>
-      <c r="JR2">
-        <v>215925</v>
-      </c>
-      <c r="JS2">
-        <v>157730</v>
-      </c>
-      <c r="JT2">
-        <v>130607</v>
-      </c>
-      <c r="JU2">
-        <v>198574</v>
-      </c>
-      <c r="JV2">
-        <v>155808</v>
-      </c>
-      <c r="JW2">
-        <v>102975</v>
-      </c>
-      <c r="JX2">
-        <v>25814</v>
-      </c>
-      <c r="JY2">
-        <v>22963</v>
-      </c>
-      <c r="JZ2">
-        <v>21697</v>
-      </c>
-      <c r="KA2">
-        <v>23751</v>
-      </c>
-      <c r="KB2">
-        <v>20350</v>
-      </c>
-      <c r="KC2">
-        <v>21671</v>
-      </c>
-      <c r="KD2">
-        <v>145483</v>
-      </c>
-      <c r="KE2">
-        <v>114435</v>
-      </c>
-      <c r="KF2">
-        <v>89879</v>
-      </c>
-      <c r="KG2">
-        <v>136439</v>
-      </c>
-      <c r="KH2">
-        <v>112449</v>
-      </c>
-      <c r="KI2">
-        <v>97966</v>
-      </c>
-      <c r="KJ2">
-        <v>137274</v>
-      </c>
-      <c r="KK2">
-        <v>121550</v>
-      </c>
-      <c r="KL2">
-        <v>96574</v>
-      </c>
-      <c r="KM2">
-        <v>133732</v>
-      </c>
-      <c r="KN2">
-        <v>113365</v>
-      </c>
-      <c r="KO2">
-        <v>62546</v>
-      </c>
-      <c r="KP2">
-        <v>44150</v>
-      </c>
-      <c r="KQ2">
-        <v>27697</v>
-      </c>
-      <c r="KR2">
-        <v>22767</v>
-      </c>
-      <c r="KS2">
-        <v>41305</v>
-      </c>
-      <c r="KT2">
-        <v>28602</v>
-      </c>
-      <c r="KU2">
-        <v>23246</v>
-      </c>
-      <c r="KV2">
-        <v>36778</v>
-      </c>
-      <c r="KW2">
-        <v>23715</v>
-      </c>
-      <c r="KX2">
-        <v>26729</v>
-      </c>
-      <c r="KY2">
-        <v>34798</v>
-      </c>
-      <c r="KZ2">
-        <v>21252</v>
-      </c>
-      <c r="LA2">
-        <v>33003</v>
-      </c>
-      <c r="LB2">
-        <v>130557</v>
-      </c>
-      <c r="LC2">
-        <v>95548</v>
-      </c>
-      <c r="LD2">
-        <v>84836</v>
-      </c>
-      <c r="LE2">
-        <v>120597</v>
-      </c>
-      <c r="LF2">
-        <v>91507</v>
-      </c>
-      <c r="LG2">
-        <v>72646</v>
-      </c>
-      <c r="LH2">
-        <v>87421</v>
-      </c>
-      <c r="LI2">
-        <v>75923</v>
-      </c>
-      <c r="LJ2">
-        <v>70468</v>
-      </c>
-      <c r="LK2">
-        <v>85658</v>
-      </c>
-      <c r="LL2">
-        <v>76592</v>
-      </c>
-      <c r="LM2">
-        <v>58221</v>
-      </c>
-      <c r="LN2">
-        <v>75703</v>
-      </c>
-      <c r="LO2">
-        <v>51359</v>
-      </c>
-      <c r="LP2">
-        <v>40208</v>
-      </c>
-      <c r="LQ2">
-        <v>72072</v>
-      </c>
-      <c r="LR2">
-        <v>55554</v>
-      </c>
-      <c r="LS2">
-        <v>31042</v>
-      </c>
-      <c r="LT2">
-        <v>146755</v>
-      </c>
-      <c r="LU2">
-        <v>104274</v>
-      </c>
-      <c r="LV2">
-        <v>103329</v>
-      </c>
-      <c r="LW2">
-        <v>142211</v>
-      </c>
-      <c r="LX2">
-        <v>108142</v>
-      </c>
-      <c r="LY2">
-        <v>83832</v>
-      </c>
-      <c r="LZ2">
-        <v>98438</v>
-      </c>
-      <c r="MA2">
-        <v>87525</v>
-      </c>
-      <c r="MB2">
-        <v>81910</v>
-      </c>
-      <c r="MC2">
-        <v>94635</v>
-      </c>
-      <c r="MD2">
-        <v>79012</v>
-      </c>
-      <c r="ME2">
-        <v>68002</v>
-      </c>
-      <c r="MF2">
-        <v>122597</v>
-      </c>
-      <c r="MG2">
-        <v>83527</v>
-      </c>
-      <c r="MH2">
-        <v>88003</v>
-      </c>
-      <c r="MI2">
-        <v>117368</v>
-      </c>
-      <c r="MJ2">
-        <v>84337</v>
-      </c>
-      <c r="MK2">
-        <v>72112</v>
-      </c>
-      <c r="ML2">
-        <v>96070</v>
-      </c>
-      <c r="MM2">
-        <v>93480</v>
-      </c>
-      <c r="MN2">
-        <v>61791</v>
-      </c>
-      <c r="MO2">
-        <v>86757</v>
-      </c>
-      <c r="MP2">
-        <v>79588</v>
-      </c>
-      <c r="MQ2">
-        <v>38405</v>
-      </c>
-      <c r="MR2">
-        <v>48602</v>
-      </c>
-      <c r="MS2">
-        <v>31910</v>
-      </c>
-      <c r="MT2">
-        <v>29067</v>
-      </c>
-      <c r="MU2">
-        <v>46360</v>
-      </c>
-      <c r="MV2">
-        <v>34699</v>
-      </c>
-      <c r="MW2">
-        <v>25654</v>
-      </c>
-      <c r="MX2">
-        <v>72444</v>
-      </c>
-      <c r="MY2">
-        <v>52242</v>
-      </c>
-      <c r="MZ2">
-        <v>35022</v>
-      </c>
-      <c r="NA2">
-        <v>69650</v>
-      </c>
-      <c r="NB2">
-        <v>54680</v>
-      </c>
-      <c r="NC2">
-        <v>36020</v>
-      </c>
-      <c r="ND2">
-        <v>59378</v>
-      </c>
-      <c r="NE2">
-        <v>37586</v>
-      </c>
-      <c r="NF2">
-        <v>42360</v>
-      </c>
-      <c r="NG2">
-        <v>56540</v>
-      </c>
-      <c r="NH2">
-        <v>35832</v>
-      </c>
-      <c r="NI2">
-        <v>50786</v>
-      </c>
-      <c r="NJ2">
-        <v>100227</v>
-      </c>
-      <c r="NK2">
-        <v>66376</v>
-      </c>
-      <c r="NL2">
-        <v>50626</v>
-      </c>
-      <c r="NM2">
-        <v>94208</v>
-      </c>
-      <c r="NN2">
-        <v>71272</v>
-      </c>
-      <c r="NO2">
-        <v>45630</v>
-      </c>
-      <c r="NP2">
-        <v>91181</v>
-      </c>
-      <c r="NQ2">
-        <v>59303</v>
-      </c>
-      <c r="NR2">
-        <v>39027</v>
-      </c>
-      <c r="NS2">
-        <v>88479</v>
-      </c>
-      <c r="NT2">
-        <v>66391</v>
-      </c>
-      <c r="NU2">
-        <v>40671</v>
-      </c>
-      <c r="NV2">
-        <v>30503</v>
-      </c>
-      <c r="NW2">
-        <v>19829</v>
-      </c>
-      <c r="NX2">
-        <v>13107</v>
-      </c>
-      <c r="NY2">
-        <v>29112</v>
-      </c>
-      <c r="NZ2">
-        <v>20476</v>
-      </c>
-      <c r="OA2">
-        <v>12911</v>
-      </c>
-      <c r="OB2">
-        <v>79315</v>
-      </c>
-      <c r="OC2">
-        <v>63798</v>
-      </c>
-      <c r="OD2">
-        <v>53846</v>
-      </c>
-      <c r="OE2">
-        <v>74829</v>
-      </c>
-      <c r="OF2">
-        <v>61116</v>
-      </c>
-      <c r="OG2">
-        <v>36923</v>
-      </c>
-      <c r="OH2">
-        <v>50230</v>
-      </c>
-      <c r="OI2">
-        <v>39812</v>
-      </c>
-      <c r="OJ2">
-        <v>42074</v>
-      </c>
-      <c r="OK2">
-        <v>48085</v>
-      </c>
-      <c r="OL2">
-        <v>37651</v>
-      </c>
-      <c r="OM2">
-        <v>36889</v>
-      </c>
-      <c r="ON2">
-        <v>139994</v>
-      </c>
-      <c r="OO2">
-        <v>110911</v>
-      </c>
-      <c r="OP2">
-        <v>96878</v>
-      </c>
-      <c r="OQ2">
-        <v>128293</v>
-      </c>
-      <c r="OR2">
-        <v>105818</v>
-      </c>
-      <c r="OS2">
-        <v>71496</v>
-      </c>
-      <c r="OT2">
-        <v>85630</v>
-      </c>
-      <c r="OU2">
-        <v>70742</v>
-      </c>
-      <c r="OV2">
-        <v>54402</v>
-      </c>
-      <c r="OW2">
-        <v>81554</v>
-      </c>
-      <c r="OX2">
-        <v>65720</v>
-      </c>
-      <c r="OY2">
-        <v>51107</v>
-      </c>
-      <c r="OZ2">
-        <v>56827</v>
-      </c>
-      <c r="PA2">
-        <v>37174</v>
-      </c>
-      <c r="PB2">
-        <v>40305</v>
-      </c>
-      <c r="PC2">
-        <v>52973</v>
-      </c>
-      <c r="PD2">
-        <v>35499</v>
-      </c>
-      <c r="PE2">
-        <v>44166</v>
-      </c>
-      <c r="PF2">
-        <v>74817</v>
-      </c>
-      <c r="PG2">
-        <v>75715</v>
-      </c>
-      <c r="PH2">
-        <v>66688</v>
-      </c>
-      <c r="PI2">
-        <v>70630</v>
-      </c>
-      <c r="PJ2">
-        <v>70424</v>
-      </c>
-      <c r="PK2">
-        <v>63044</v>
-      </c>
-      <c r="PL2">
-        <v>174209</v>
-      </c>
-      <c r="PM2">
-        <v>136401</v>
-      </c>
-      <c r="PN2">
-        <v>112743</v>
-      </c>
-      <c r="PO2">
-        <v>169615</v>
-      </c>
-      <c r="PP2">
-        <v>133521</v>
-      </c>
-      <c r="PQ2">
-        <v>86116</v>
-      </c>
-      <c r="PR2">
-        <v>97870</v>
-      </c>
-      <c r="PS2">
-        <v>63845</v>
-      </c>
-      <c r="PT2">
-        <v>45676</v>
-      </c>
-      <c r="PU2">
-        <v>93707</v>
-      </c>
-      <c r="PV2">
-        <v>69490</v>
-      </c>
-      <c r="PW2">
-        <v>44774</v>
-      </c>
-      <c r="PX2">
-        <v>51625</v>
-      </c>
-      <c r="PY2">
-        <v>53599</v>
-      </c>
-      <c r="PZ2">
-        <v>47327</v>
       </c>
       <c r="QA2">
         <v>46521</v>
